--- a/data/canary/valcan_pack_2026-04-12/_VALCAN_2026/30_FIELD_ENGINEERING/valcanary_service_event_tracker_2024.xlsx
+++ b/data/canary/valcan_pack_2026-04-12/_VALCAN_2026/30_FIELD_ENGINEERING/valcanary_service_event_tracker_2024.xlsx
@@ -596,7 +596,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VALEVT-2024-001</t>
+          <t>Event 2024-001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -606,7 +606,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VALSITE-ALPHA</t>
+          <t>Site: Validation Alpha Site</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>VALPART-UPS48V-003; VALPART-FLT-009</t>
+          <t>QZ-3003; QZ-3009</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -638,7 +638,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VALEVT-2024-002</t>
+          <t>Event 2024-002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VALSITE-BRAVO</t>
+          <t>Site: Validation Bravo Site</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>VALPART-GPSANT-004</t>
+          <t>QZ-3004</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -680,7 +680,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VALEVT-2024-003</t>
+          <t>Event 2024-003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>VALSITE-CHARLIE</t>
+          <t>Site: Validation Charlie Site</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>VALPART-FAN-006; VALPART-UPSCARD-015</t>
+          <t>QZ-3006; QZ-3015</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -722,7 +722,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VALEVT-2024-004</t>
+          <t>Event 2024-004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VALSITE-ALPHA</t>
+          <t>Site: Validation Alpha Site</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>VALPART-UPS48V-003</t>
+          <t>QZ-3003</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -764,7 +764,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VALEVT-2024-005</t>
+          <t>Event 2024-005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>VALSITE-DELTA</t>
+          <t>Site: Validation Delta Site</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>VALPART-PSU-008</t>
+          <t>QZ-3008</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -806,7 +806,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>VALEVT-2024-006</t>
+          <t>Event 2024-006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>VALSITE-ECHO</t>
+          <t>Site: Validation Echo Site</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -848,7 +848,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VALEVT-2024-007</t>
+          <t>Event 2024-007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>VALSITE-BRAVO</t>
+          <t>Site: Validation Bravo Site</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -890,7 +890,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VALEVT-2024-008</t>
+          <t>Event 2024-008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>VALSITE-DELTA</t>
+          <t>Site: Validation Delta Site</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>VALPART-BATT-007</t>
+          <t>QZ-3007</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -932,7 +932,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VALEVT-2024-009</t>
+          <t>Event 2024-009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>VALSITE-DELTA</t>
+          <t>Site: Validation Delta Site</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -974,7 +974,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VALEVT-2024-010</t>
+          <t>Event 2024-010</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>VALSITE-ECHO</t>
+          <t>Site: Validation Echo Site</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>VALPART-COUPLER-012</t>
+          <t>QZ-3012</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1016,7 +1016,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>VALEVT-2024-011</t>
+          <t>Event 2024-011</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>VALSITE-CHARLIE</t>
+          <t>Site: Validation Charlie Site</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>VALPART-NIC-013</t>
+          <t>QZ-3013</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
